--- a/sacko_Ex3A_tables.xlsx
+++ b/sacko_Ex3A_tables.xlsx
@@ -1,13 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maya\Documents\DATA_Labs\W2_Workshop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1A0735-2DB4-4BF3-B991-D8961FD4CA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="customers" sheetId="1" r:id="rId1"/>
+    <sheet name="dogs" sheetId="2" r:id="rId2"/>
+    <sheet name="appointments" sheetId="3" r:id="rId3"/>
+    <sheet name="payments" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,9 +27,299 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="95">
+  <si>
+    <t>customer_name</t>
+  </si>
+  <si>
+    <t>phone_number</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> email</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>dog_id</t>
+  </si>
+  <si>
+    <t>dog_name</t>
+  </si>
+  <si>
+    <t>breed</t>
+  </si>
+  <si>
+    <t>emergency_contact_name</t>
+  </si>
+  <si>
+    <t>emergency_contact_phone</t>
+  </si>
+  <si>
+    <t> customer_id</t>
+  </si>
+  <si>
+    <t>appointment_id</t>
+  </si>
+  <si>
+    <t>appointment_date</t>
+  </si>
+  <si>
+    <t>start_time</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>payment_date</t>
+  </si>
+  <si>
+    <t>payment_status</t>
+  </si>
+  <si>
+    <t>payment_id</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>payment_method</t>
+  </si>
+  <si>
+    <t>duration_time_min</t>
+  </si>
+  <si>
+    <t>customer_id</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>Ola</t>
+  </si>
+  <si>
+    <t>Lora</t>
+  </si>
+  <si>
+    <t>Jary</t>
+  </si>
+  <si>
+    <t>Oscar</t>
+  </si>
+  <si>
+    <t>Lisa</t>
+  </si>
+  <si>
+    <t>555-555-551</t>
+  </si>
+  <si>
+    <t>555-555-552</t>
+  </si>
+  <si>
+    <t>555-555-553</t>
+  </si>
+  <si>
+    <t>555-555-554</t>
+  </si>
+  <si>
+    <t>555-555-555</t>
+  </si>
+  <si>
+    <t>555-555-556</t>
+  </si>
+  <si>
+    <t>Alex@example.com</t>
+  </si>
+  <si>
+    <t>Ola@example.com</t>
+  </si>
+  <si>
+    <t>Lora@example.com</t>
+  </si>
+  <si>
+    <t>Jary@example.com</t>
+  </si>
+  <si>
+    <t>Oscar@example.com</t>
+  </si>
+  <si>
+    <t>Lisa@example.com</t>
+  </si>
+  <si>
+    <t>771 S Candy street, NJ 07001</t>
+  </si>
+  <si>
+    <t>772 S Candy street, NJ 07002</t>
+  </si>
+  <si>
+    <t>773 S Candy street, NJ 07003</t>
+  </si>
+  <si>
+    <t>774 S Candy street, NJ 07004</t>
+  </si>
+  <si>
+    <t>775 S Candy street, NJ 07005</t>
+  </si>
+  <si>
+    <t>776 S Candy street, NJ 07006</t>
+  </si>
+  <si>
+    <t>Milou</t>
+  </si>
+  <si>
+    <t>Rex</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brwon </t>
+  </si>
+  <si>
+    <t>Police</t>
+  </si>
+  <si>
+    <t>Labrador Retriever</t>
+  </si>
+  <si>
+    <t>German Shepherd</t>
+  </si>
+  <si>
+    <t>Chihuahua</t>
+  </si>
+  <si>
+    <t>Poodle</t>
+  </si>
+  <si>
+    <t>age_months</t>
+  </si>
+  <si>
+    <t>Felix</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>card</t>
+  </si>
+  <si>
+    <t>zelle</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>paid</t>
+  </si>
+  <si>
+    <t>refunded</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>555-555-557</t>
+  </si>
+  <si>
+    <t>777 S Candy street, NJ 07007</t>
+  </si>
+  <si>
+    <t>Noah</t>
+  </si>
+  <si>
+    <t>555-555-558</t>
+  </si>
+  <si>
+    <t>778 S Candy street, NJ 07008</t>
+  </si>
+  <si>
+    <t>Zara</t>
+  </si>
+  <si>
+    <t>555-555-559</t>
+  </si>
+  <si>
+    <t>779 S Candy street, NJ 07009</t>
+  </si>
+  <si>
+    <t>Ben</t>
+  </si>
+  <si>
+    <t>555-555-560</t>
+  </si>
+  <si>
+    <t>780 S Candy street, NJ 07010</t>
+  </si>
+  <si>
+    <t>Nina</t>
+  </si>
+  <si>
+    <t>555-555-561</t>
+  </si>
+  <si>
+    <t>781 S Candy street, NJ 07011</t>
+  </si>
+  <si>
+    <t>Avie</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May@example.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah@example.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zara@example.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben@example.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nina@example.com </t>
+  </si>
+  <si>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>Golden Retriever</t>
+  </si>
+  <si>
+    <t>Charlie</t>
+  </si>
+  <si>
+    <t>Beagle</t>
+  </si>
+  <si>
+    <t>Luna</t>
+  </si>
+  <si>
+    <t>Bulldog</t>
+  </si>
+  <si>
+    <t>Coco</t>
+  </si>
+  <si>
+    <t>Dachshund</t>
+  </si>
+  <si>
+    <t>Buddy</t>
+  </si>
+  <si>
+    <t>Boxer</t>
+  </si>
+  <si>
+    <t>venmo</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,13 +327,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2328"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,13 +372,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,10 +668,1042 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.36328125" customWidth="1"/>
+    <col min="5" max="5" width="24.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{9BA62785-6E7C-4C1B-B171-056941BDE2EB}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{944B4527-328B-4652-8312-3A95B0374FB2}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{837BAACE-CD5A-4019-933E-6EA50A82253A}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{DDDB19FE-05AC-45A8-ACA3-F62653116146}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{FAB8FD13-79FF-48EA-BA7D-AFE423E44908}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{B16F07FB-23EE-4C3A-A7E3-C39CC86402A1}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{3C33C8EE-F544-4D91-822F-23D445D579ED}"/>
+    <hyperlink ref="D9" r:id="rId8" xr:uid="{D48A8289-8C52-4567-95E2-A524AEC99FDD}"/>
+    <hyperlink ref="D10" r:id="rId9" xr:uid="{AC525308-166A-407D-985A-D37F6DE3E1ED}"/>
+    <hyperlink ref="D11" r:id="rId10" xr:uid="{4719730A-8A27-44A6-B26C-BD67FF2BD104}"/>
+    <hyperlink ref="D12" r:id="rId11" xr:uid="{B62D0C3F-6144-4703-BE0D-265F9BA442A2}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A98E84-E3DC-4F45-B493-2D34E1C6A63A}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3">
+        <v>60</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10">
+        <v>72</v>
+      </c>
+      <c r="E10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AE4086C-56CF-49D1-8574-37EF7ACEBBF8}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7">
+        <v>46256</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E2">
+        <v>180</v>
+      </c>
+      <c r="F2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="7">
+        <v>46290</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E3">
+        <v>120</v>
+      </c>
+      <c r="F3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" s="7">
+        <v>46294</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E4">
+        <v>120</v>
+      </c>
+      <c r="F4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="7">
+        <v>46316</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E5">
+        <v>120</v>
+      </c>
+      <c r="F5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" s="7">
+        <v>46324</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E6">
+        <v>120</v>
+      </c>
+      <c r="F6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" s="7">
+        <v>46324</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="E7">
+        <v>120</v>
+      </c>
+      <c r="F7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" s="7">
+        <v>46325</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E8">
+        <v>120</v>
+      </c>
+      <c r="F8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" s="7">
+        <v>46329</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E9">
+        <v>180</v>
+      </c>
+      <c r="F9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>46331</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E10">
+        <v>120</v>
+      </c>
+      <c r="F10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7">
+        <v>46336</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E11">
+        <v>60</v>
+      </c>
+      <c r="F11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" s="7">
+        <v>46338</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="E12">
+        <v>120</v>
+      </c>
+      <c r="F12">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BCA3FAC-1999-4CA2-9605-E86F1E083B11}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>90</v>
+      </c>
+      <c r="D2" s="7">
+        <v>46264</v>
+      </c>
+      <c r="E2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>60</v>
+      </c>
+      <c r="D3" s="7">
+        <v>46295</v>
+      </c>
+      <c r="E3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>60</v>
+      </c>
+      <c r="D4" s="7">
+        <v>46295</v>
+      </c>
+      <c r="E4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>60</v>
+      </c>
+      <c r="D5" s="7">
+        <v>46325</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>60</v>
+      </c>
+      <c r="D6" s="7">
+        <v>46325</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>60</v>
+      </c>
+      <c r="D7" s="7">
+        <v>46325</v>
+      </c>
+      <c r="E7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>60</v>
+      </c>
+      <c r="D8" s="7">
+        <v>46356</v>
+      </c>
+      <c r="E8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>90</v>
+      </c>
+      <c r="D9" s="7">
+        <v>46356</v>
+      </c>
+      <c r="E9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>60</v>
+      </c>
+      <c r="D10" s="7">
+        <v>46356</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>30</v>
+      </c>
+      <c r="D11" s="7">
+        <v>46356</v>
+      </c>
+      <c r="E11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>60</v>
+      </c>
+      <c r="D12" s="7">
+        <v>46356</v>
+      </c>
+      <c r="E12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>